--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2024_magallanes.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2024_magallanes.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$E$341</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$E$375</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">territorio</t>
   </si>
@@ -105,6 +105,9 @@
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
+    <t xml:space="preserve">Antártica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Porvenir</t>
   </si>
   <si>
@@ -129,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:19</t>
+    <t xml:space="preserve">2026-08-28 11:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -141,16 +144,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_comunal_piramide_2024_magallanes.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Piramide de poblacion (comunal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Magallanes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
   </si>
 </sst>
 </file>
@@ -3440,10 +3452,10 @@
         <v>7</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -3457,10 +3469,10 @@
         <v>8</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -3474,10 +3486,10 @@
         <v>9</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -3491,10 +3503,10 @@
         <v>10</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -3508,10 +3520,10 @@
         <v>11</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -3525,10 +3537,10 @@
         <v>12</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>279</v>
+        <v>1</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="178">
@@ -3542,10 +3554,10 @@
         <v>13</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>329</v>
+        <v>1</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="179">
@@ -3559,10 +3571,10 @@
         <v>14</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>345</v>
+        <v>1</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="180">
@@ -3576,10 +3588,10 @@
         <v>15</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -3593,10 +3605,10 @@
         <v>16</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -3610,10 +3622,10 @@
         <v>17</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -3627,10 +3639,10 @@
         <v>18</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -3644,10 +3656,10 @@
         <v>19</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -3661,10 +3673,10 @@
         <v>20</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -3678,10 +3690,10 @@
         <v>21</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -3695,10 +3707,10 @@
         <v>22</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -3712,10 +3724,10 @@
         <v>23</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -3729,10 +3741,10 @@
         <v>7</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -3746,10 +3758,10 @@
         <v>8</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -3763,10 +3775,10 @@
         <v>9</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -3780,10 +3792,10 @@
         <v>10</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -3797,10 +3809,10 @@
         <v>11</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -3814,10 +3826,10 @@
         <v>12</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="195">
@@ -3831,10 +3843,10 @@
         <v>13</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>389</v>
+        <v>2</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="196">
@@ -3848,10 +3860,10 @@
         <v>14</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>323</v>
+        <v>3</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="197">
@@ -3865,10 +3877,10 @@
         <v>15</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>279</v>
+        <v>2</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="198">
@@ -3882,10 +3894,10 @@
         <v>16</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>242</v>
+        <v>1</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>0.03</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="199">
@@ -3899,10 +3911,10 @@
         <v>17</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -3916,10 +3928,10 @@
         <v>18</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>238</v>
+        <v>1</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>0.03</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="201">
@@ -3933,10 +3945,10 @@
         <v>19</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -3950,10 +3962,10 @@
         <v>20</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -3967,10 +3979,10 @@
         <v>21</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>0.02</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="204">
@@ -3984,10 +3996,10 @@
         <v>22</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -4001,10 +4013,10 @@
         <v>23</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -4018,10 +4030,10 @@
         <v>7</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>7</v>
+        <v>166</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="207">
@@ -4035,7 +4047,7 @@
         <v>8</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>0.03</v>
@@ -4052,10 +4064,10 @@
         <v>9</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>28</v>
+        <v>254</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="209">
@@ -4069,10 +4081,10 @@
         <v>10</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>13</v>
+        <v>221</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="210">
@@ -4086,7 +4098,7 @@
         <v>11</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>12</v>
+        <v>185</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>0.02</v>
@@ -4103,10 +4115,10 @@
         <v>12</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>8</v>
+        <v>279</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="212">
@@ -4120,10 +4132,10 @@
         <v>13</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>26</v>
+        <v>329</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="213">
@@ -4137,10 +4149,10 @@
         <v>14</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>13</v>
+        <v>345</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="214">
@@ -4154,7 +4166,7 @@
         <v>15</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>17</v>
+        <v>252</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>0.03</v>
@@ -4171,10 +4183,10 @@
         <v>16</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>10</v>
+        <v>219</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="216">
@@ -4188,10 +4200,10 @@
         <v>17</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>13</v>
+        <v>208</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="217">
@@ -4205,7 +4217,7 @@
         <v>18</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>0.03</v>
@@ -4222,10 +4234,10 @@
         <v>19</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>14</v>
+        <v>178</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="219">
@@ -4239,10 +4251,10 @@
         <v>20</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>14</v>
+        <v>163</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="220">
@@ -4256,10 +4268,10 @@
         <v>21</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="221">
@@ -4273,10 +4285,10 @@
         <v>22</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="222">
@@ -4290,10 +4302,10 @@
         <v>23</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="223">
@@ -4307,10 +4319,10 @@
         <v>7</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="224">
@@ -4324,10 +4336,10 @@
         <v>8</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>22</v>
+        <v>208</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="225">
@@ -4341,10 +4353,10 @@
         <v>9</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="226">
@@ -4358,10 +4370,10 @@
         <v>10</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>19</v>
+        <v>250</v>
       </c>
       <c r="E226" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="227">
@@ -4375,10 +4387,10 @@
         <v>11</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>19</v>
+        <v>232</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="228">
@@ -4392,7 +4404,7 @@
         <v>12</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>21</v>
+        <v>301</v>
       </c>
       <c r="E228" s="2" t="n">
         <v>0.04</v>
@@ -4409,10 +4421,10 @@
         <v>13</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>23</v>
+        <v>389</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="230">
@@ -4426,7 +4438,7 @@
         <v>14</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="E230" s="2" t="n">
         <v>0.04</v>
@@ -4443,10 +4455,10 @@
         <v>15</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>12</v>
+        <v>279</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="232">
@@ -4460,7 +4472,7 @@
         <v>16</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>16</v>
+        <v>242</v>
       </c>
       <c r="E232" s="2" t="n">
         <v>0.03</v>
@@ -4477,7 +4489,7 @@
         <v>17</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>16</v>
+        <v>255</v>
       </c>
       <c r="E233" s="2" t="n">
         <v>0.03</v>
@@ -4494,10 +4506,10 @@
         <v>18</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>27</v>
+        <v>238</v>
       </c>
       <c r="E234" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="235">
@@ -4511,10 +4523,10 @@
         <v>19</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>23</v>
+        <v>236</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="236">
@@ -4528,10 +4540,10 @@
         <v>20</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="237">
@@ -4545,10 +4557,10 @@
         <v>21</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="E237" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="238">
@@ -4562,7 +4574,7 @@
         <v>22</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="E238" s="2" t="n">
         <v>0.01</v>
@@ -4579,10 +4591,10 @@
         <v>23</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="240">
@@ -4596,10 +4608,10 @@
         <v>7</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E240" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="241">
@@ -4613,10 +4625,10 @@
         <v>8</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E241" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="242">
@@ -4630,10 +4642,10 @@
         <v>9</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E242" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="243">
@@ -4647,7 +4659,7 @@
         <v>10</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E243" s="2" t="n">
         <v>0.02</v>
@@ -4664,10 +4676,10 @@
         <v>11</v>
       </c>
       <c r="D244" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E244" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="245">
@@ -4681,10 +4693,10 @@
         <v>12</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E245" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="246">
@@ -4698,10 +4710,10 @@
         <v>13</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E246" s="2" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="247">
@@ -4715,7 +4727,7 @@
         <v>14</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E247" s="2" t="n">
         <v>0.02</v>
@@ -4732,10 +4744,10 @@
         <v>15</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E248" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="249">
@@ -4749,10 +4761,10 @@
         <v>16</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E249" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="250">
@@ -4766,10 +4778,10 @@
         <v>17</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E250" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="251">
@@ -4783,10 +4795,10 @@
         <v>18</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E251" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="252">
@@ -4800,7 +4812,7 @@
         <v>19</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E252" s="2" t="n">
         <v>0.03</v>
@@ -4817,10 +4829,10 @@
         <v>20</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E253" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="254">
@@ -4834,10 +4846,10 @@
         <v>21</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E254" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="255">
@@ -4854,7 +4866,7 @@
         <v>2</v>
       </c>
       <c r="E255" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -4868,10 +4880,10 @@
         <v>23</v>
       </c>
       <c r="D256" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E256" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="257">
@@ -4885,7 +4897,7 @@
         <v>7</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E257" s="2" t="n">
         <v>0.03</v>
@@ -4902,10 +4914,10 @@
         <v>8</v>
       </c>
       <c r="D258" s="2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E258" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="259">
@@ -4919,10 +4931,10 @@
         <v>9</v>
       </c>
       <c r="D259" s="2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E259" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="260">
@@ -4936,10 +4948,10 @@
         <v>10</v>
       </c>
       <c r="D260" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="261">
@@ -4953,10 +4965,10 @@
         <v>11</v>
       </c>
       <c r="D261" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E261" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="262">
@@ -4970,7 +4982,7 @@
         <v>12</v>
       </c>
       <c r="D262" s="2" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E262" s="2" t="n">
         <v>0.04</v>
@@ -4987,10 +4999,10 @@
         <v>13</v>
       </c>
       <c r="D263" s="2" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E263" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="264">
@@ -5004,10 +5016,10 @@
         <v>14</v>
       </c>
       <c r="D264" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E264" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="265">
@@ -5021,10 +5033,10 @@
         <v>15</v>
       </c>
       <c r="D265" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E265" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="266">
@@ -5038,10 +5050,10 @@
         <v>16</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E266" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="267">
@@ -5055,10 +5067,10 @@
         <v>17</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E267" s="2" t="n">
-        <v>0.07</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="268">
@@ -5072,10 +5084,10 @@
         <v>18</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="E268" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="269">
@@ -5089,10 +5101,10 @@
         <v>19</v>
       </c>
       <c r="D269" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E269" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="270">
@@ -5106,10 +5118,10 @@
         <v>20</v>
       </c>
       <c r="D270" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E270" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="271">
@@ -5123,10 +5135,10 @@
         <v>21</v>
       </c>
       <c r="D271" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="272">
@@ -5140,7 +5152,7 @@
         <v>22</v>
       </c>
       <c r="D272" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E272" s="2" t="n">
         <v>0.01</v>
@@ -5157,10 +5169,10 @@
         <v>23</v>
       </c>
       <c r="D273" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E273" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="274">
@@ -5174,7 +5186,7 @@
         <v>7</v>
       </c>
       <c r="D274" s="2" t="n">
-        <v>608</v>
+        <v>4</v>
       </c>
       <c r="E274" s="2" t="n">
         <v>0.02</v>
@@ -5191,10 +5203,10 @@
         <v>8</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>741</v>
+        <v>9</v>
       </c>
       <c r="E275" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="276">
@@ -5208,10 +5220,10 @@
         <v>9</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>863</v>
+        <v>4</v>
       </c>
       <c r="E276" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="277">
@@ -5225,10 +5237,10 @@
         <v>10</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>849</v>
+        <v>4</v>
       </c>
       <c r="E277" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="278">
@@ -5242,7 +5254,7 @@
         <v>11</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>840</v>
+        <v>6</v>
       </c>
       <c r="E278" s="2" t="n">
         <v>0.03</v>
@@ -5259,10 +5271,10 @@
         <v>12</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>1122</v>
+        <v>5</v>
       </c>
       <c r="E279" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="280">
@@ -5276,10 +5288,10 @@
         <v>13</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>1436</v>
+        <v>14</v>
       </c>
       <c r="E280" s="2" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="281">
@@ -5293,10 +5305,10 @@
         <v>14</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>1255</v>
+        <v>4</v>
       </c>
       <c r="E281" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="282">
@@ -5310,10 +5322,10 @@
         <v>15</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>1021</v>
+        <v>4</v>
       </c>
       <c r="E282" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="283">
@@ -5327,7 +5339,7 @@
         <v>16</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>968</v>
+        <v>5</v>
       </c>
       <c r="E283" s="2" t="n">
         <v>0.03</v>
@@ -5344,7 +5356,7 @@
         <v>17</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>851</v>
+        <v>6</v>
       </c>
       <c r="E284" s="2" t="n">
         <v>0.03</v>
@@ -5361,10 +5373,10 @@
         <v>18</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>794</v>
+        <v>2</v>
       </c>
       <c r="E285" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="286">
@@ -5378,7 +5390,7 @@
         <v>19</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>743</v>
+        <v>5</v>
       </c>
       <c r="E286" s="2" t="n">
         <v>0.03</v>
@@ -5395,10 +5407,10 @@
         <v>20</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>689</v>
+        <v>2</v>
       </c>
       <c r="E287" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="288">
@@ -5412,10 +5424,10 @@
         <v>21</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>565</v>
+        <v>0</v>
       </c>
       <c r="E288" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -5429,7 +5441,7 @@
         <v>22</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>424</v>
+        <v>2</v>
       </c>
       <c r="E289" s="2" t="n">
         <v>0.01</v>
@@ -5446,10 +5458,10 @@
         <v>23</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>608</v>
+        <v>0</v>
       </c>
       <c r="E290" s="2" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -5463,10 +5475,10 @@
         <v>7</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>658</v>
+        <v>5</v>
       </c>
       <c r="E291" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="292">
@@ -5480,10 +5492,10 @@
         <v>8</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>745</v>
+        <v>4</v>
       </c>
       <c r="E292" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="293">
@@ -5497,10 +5509,10 @@
         <v>9</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>888</v>
+        <v>9</v>
       </c>
       <c r="E293" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="294">
@@ -5514,10 +5526,10 @@
         <v>10</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>936</v>
+        <v>2</v>
       </c>
       <c r="E294" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="295">
@@ -5531,10 +5543,10 @@
         <v>11</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>846</v>
+        <v>4</v>
       </c>
       <c r="E295" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="296">
@@ -5548,7 +5560,7 @@
         <v>12</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>1144</v>
+        <v>7</v>
       </c>
       <c r="E296" s="2" t="n">
         <v>0.04</v>
@@ -5565,10 +5577,10 @@
         <v>13</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>1386</v>
+        <v>13</v>
       </c>
       <c r="E297" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="298">
@@ -5582,10 +5594,10 @@
         <v>14</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>1406</v>
+        <v>10</v>
       </c>
       <c r="E298" s="2" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="299">
@@ -5599,10 +5611,10 @@
         <v>15</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>1175</v>
+        <v>5</v>
       </c>
       <c r="E299" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="300">
@@ -5616,10 +5628,10 @@
         <v>16</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>1026</v>
+        <v>4</v>
       </c>
       <c r="E300" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="301">
@@ -5633,10 +5645,10 @@
         <v>17</v>
       </c>
       <c r="D301" s="2" t="n">
-        <v>972</v>
+        <v>12</v>
       </c>
       <c r="E301" s="2" t="n">
-        <v>0.03</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="302">
@@ -5650,10 +5662,10 @@
         <v>18</v>
       </c>
       <c r="D302" s="2" t="n">
-        <v>838</v>
+        <v>4</v>
       </c>
       <c r="E302" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="303">
@@ -5667,10 +5679,10 @@
         <v>19</v>
       </c>
       <c r="D303" s="2" t="n">
-        <v>745</v>
+        <v>10</v>
       </c>
       <c r="E303" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="304">
@@ -5684,7 +5696,7 @@
         <v>20</v>
       </c>
       <c r="D304" s="2" t="n">
-        <v>681</v>
+        <v>3</v>
       </c>
       <c r="E304" s="2" t="n">
         <v>0.02</v>
@@ -5701,7 +5713,7 @@
         <v>21</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>618</v>
+        <v>4</v>
       </c>
       <c r="E305" s="2" t="n">
         <v>0.02</v>
@@ -5718,7 +5730,7 @@
         <v>22</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>386</v>
+        <v>1</v>
       </c>
       <c r="E306" s="2" t="n">
         <v>0.01</v>
@@ -5735,10 +5747,10 @@
         <v>23</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>451</v>
+        <v>2</v>
       </c>
       <c r="E307" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="308">
@@ -5752,10 +5764,10 @@
         <v>7</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>2</v>
+        <v>608</v>
       </c>
       <c r="E308" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="309">
@@ -5769,10 +5781,10 @@
         <v>8</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>4</v>
+        <v>741</v>
       </c>
       <c r="E309" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="310">
@@ -5786,10 +5798,10 @@
         <v>9</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>3</v>
+        <v>863</v>
       </c>
       <c r="E310" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="311">
@@ -5803,7 +5815,7 @@
         <v>10</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>5</v>
+        <v>849</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>0.03</v>
@@ -5820,7 +5832,7 @@
         <v>11</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>6</v>
+        <v>840</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>0.03</v>
@@ -5837,10 +5849,10 @@
         <v>12</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>4</v>
+        <v>1122</v>
       </c>
       <c r="E313" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="314">
@@ -5854,10 +5866,10 @@
         <v>13</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>12</v>
+        <v>1436</v>
       </c>
       <c r="E314" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="315">
@@ -5871,10 +5883,10 @@
         <v>14</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>14</v>
+        <v>1255</v>
       </c>
       <c r="E315" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="316">
@@ -5888,10 +5900,10 @@
         <v>15</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>12</v>
+        <v>1021</v>
       </c>
       <c r="E316" s="2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="317">
@@ -5905,10 +5917,10 @@
         <v>16</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>9</v>
+        <v>968</v>
       </c>
       <c r="E317" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="318">
@@ -5922,10 +5934,10 @@
         <v>17</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>2</v>
+        <v>851</v>
       </c>
       <c r="E318" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="319">
@@ -5939,10 +5951,10 @@
         <v>18</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>11</v>
+        <v>794</v>
       </c>
       <c r="E319" s="2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="320">
@@ -5956,10 +5968,10 @@
         <v>19</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>3</v>
+        <v>743</v>
       </c>
       <c r="E320" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="321">
@@ -5973,10 +5985,10 @@
         <v>20</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>5</v>
+        <v>689</v>
       </c>
       <c r="E321" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="322">
@@ -5990,10 +6002,10 @@
         <v>21</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>0</v>
+        <v>565</v>
       </c>
       <c r="E322" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="323">
@@ -6007,7 +6019,7 @@
         <v>22</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>2</v>
+        <v>424</v>
       </c>
       <c r="E323" s="2" t="n">
         <v>0.01</v>
@@ -6024,10 +6036,10 @@
         <v>23</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>1</v>
+        <v>608</v>
       </c>
       <c r="E324" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="325">
@@ -6041,10 +6053,10 @@
         <v>7</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>1</v>
+        <v>658</v>
       </c>
       <c r="E325" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="326">
@@ -6058,10 +6070,10 @@
         <v>8</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>3</v>
+        <v>745</v>
       </c>
       <c r="E326" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="327">
@@ -6075,10 +6087,10 @@
         <v>9</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>4</v>
+        <v>888</v>
       </c>
       <c r="E327" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="328">
@@ -6092,10 +6104,10 @@
         <v>10</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>3</v>
+        <v>936</v>
       </c>
       <c r="E328" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="329">
@@ -6109,7 +6121,7 @@
         <v>11</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>6</v>
+        <v>846</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0.03</v>
@@ -6126,10 +6138,10 @@
         <v>12</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>9</v>
+        <v>1144</v>
       </c>
       <c r="E330" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="331">
@@ -6143,10 +6155,10 @@
         <v>13</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>12</v>
+        <v>1386</v>
       </c>
       <c r="E331" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="332">
@@ -6160,10 +6172,10 @@
         <v>14</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>13</v>
+        <v>1406</v>
       </c>
       <c r="E332" s="2" t="n">
-        <v>0.07</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="333">
@@ -6177,10 +6189,10 @@
         <v>15</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>12</v>
+        <v>1175</v>
       </c>
       <c r="E333" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="334">
@@ -6194,7 +6206,7 @@
         <v>16</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>7</v>
+        <v>1026</v>
       </c>
       <c r="E334" s="2" t="n">
         <v>0.04</v>
@@ -6211,10 +6223,10 @@
         <v>17</v>
       </c>
       <c r="D335" s="2" t="n">
-        <v>10</v>
+        <v>972</v>
       </c>
       <c r="E335" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="336">
@@ -6228,10 +6240,10 @@
         <v>18</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>11</v>
+        <v>838</v>
       </c>
       <c r="E336" s="2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="337">
@@ -6245,10 +6257,10 @@
         <v>19</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>3</v>
+        <v>745</v>
       </c>
       <c r="E337" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="338">
@@ -6262,10 +6274,10 @@
         <v>20</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>1</v>
+        <v>681</v>
       </c>
       <c r="E338" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="339">
@@ -6279,7 +6291,7 @@
         <v>21</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>3</v>
+        <v>618</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0.02</v>
@@ -6296,7 +6308,7 @@
         <v>22</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>1</v>
+        <v>386</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0.01</v>
@@ -6313,14 +6325,592 @@
         <v>23</v>
       </c>
       <c r="D341" s="2" t="n">
+        <v>451</v>
+      </c>
+      <c r="E341" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D342" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E342" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D343" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E343" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D344" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E341" s="2" t="n">
+      <c r="E344" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D345" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E345" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D346" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E346" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D347" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E347" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D348" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E348" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D349" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E349" s="2" t="n">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D350" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E350" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D351" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E351" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D352" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E352" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D353" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E353" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D354" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E354" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D355" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E355" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D357" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E357" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D358" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E358" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D359" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E359" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D360" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E360" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D361" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E361" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D362" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E362" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D363" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E363" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D364" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E364" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D365" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E365" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D366" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E366" s="2" t="n">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D367" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E367" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D368" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E368" s="2" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D369" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E369" s="2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D370" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E370" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D371" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E371" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D372" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E372" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D373" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E373" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D374" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E374" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D375" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E375" s="2" t="n">
         <v>0.02</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E341"/>
+  <autoFilter ref="A1:E375"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -6337,58 +6927,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2024_magallanes.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2024_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:17</t>
+    <t xml:space="preserve">2026-09-06 17:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
